--- a/artfynd/A 43526-2025 artfynd.xlsx
+++ b/artfynd/A 43526-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129124618</v>
       </c>
       <c r="B2" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -810,7 +810,7 @@
         <v>129124713</v>
       </c>
       <c r="B3" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 43526-2025 artfynd.xlsx
+++ b/artfynd/A 43526-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129124618</v>
       </c>
       <c r="B2" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -810,7 +810,7 @@
         <v>129124713</v>
       </c>
       <c r="B3" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 43526-2025 artfynd.xlsx
+++ b/artfynd/A 43526-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129124618</v>
       </c>
       <c r="B2" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -810,7 +810,7 @@
         <v>129124713</v>
       </c>
       <c r="B3" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 43526-2025 artfynd.xlsx
+++ b/artfynd/A 43526-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129124618</v>
       </c>
       <c r="B2" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -810,7 +810,7 @@
         <v>129124713</v>
       </c>
       <c r="B3" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 43526-2025 artfynd.xlsx
+++ b/artfynd/A 43526-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129124618</v>
       </c>
       <c r="B2" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -810,7 +810,7 @@
         <v>129124713</v>
       </c>
       <c r="B3" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 43526-2025 artfynd.xlsx
+++ b/artfynd/A 43526-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129124618</v>
       </c>
       <c r="B2" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -810,7 +810,7 @@
         <v>129124713</v>
       </c>
       <c r="B3" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
